--- a/data/trans_dic/P68-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P68-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,42; 33,22</t>
+          <t>19,94; 33,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,95; 41,73</t>
+          <t>23,5; 40,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,57; 51,81</t>
+          <t>34,58; 52,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 19,07</t>
+          <t>7,97; 18,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 34,53</t>
+          <t>18,62; 35,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,89; 44,16</t>
+          <t>24,24; 45,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,31; 50,32</t>
+          <t>31,25; 50,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 15,76</t>
+          <t>7,61; 15,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,45; 31,69</t>
+          <t>20,8; 31,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,72; 40,22</t>
+          <t>26,73; 40,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,49; 48,79</t>
+          <t>35,94; 48,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,52</t>
+          <t>8,41; 15,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,89; 33,35</t>
+          <t>21,16; 32,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,52; 40,15</t>
+          <t>26,18; 39,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,05; 57,53</t>
+          <t>40,77; 56,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,62; 28,64</t>
+          <t>14,05; 27,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,06; 32,88</t>
+          <t>17,83; 32,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,46; 37,64</t>
+          <t>20,17; 37,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,76; 46,54</t>
+          <t>28,7; 47,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,43; 35,93</t>
+          <t>22,39; 35,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 31,28</t>
+          <t>21,7; 30,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,72; 36,58</t>
+          <t>25,3; 36,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37,83; 50,0</t>
+          <t>37,87; 50,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,09; 28,92</t>
+          <t>19,56; 29,48</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,08; 27,29</t>
+          <t>14,86; 26,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,7; 24,22</t>
+          <t>11,71; 24,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 24,2</t>
+          <t>11,6; 24,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,32; 42,4</t>
+          <t>26,47; 41,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,02; 32,6</t>
+          <t>14,97; 32,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 34,08</t>
+          <t>13,84; 32,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 24,37</t>
+          <t>8,74; 24,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,62; 45,81</t>
+          <t>30,44; 45,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,0; 27,84</t>
+          <t>16,85; 27,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,55; 25,13</t>
+          <t>14,46; 25,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 21,86</t>
+          <t>12,02; 22,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,37; 41,53</t>
+          <t>30,79; 41,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,16; 32,02</t>
+          <t>20,43; 32,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,89; 42,24</t>
+          <t>25,15; 41,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,58; 37,82</t>
+          <t>20,9; 37,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 33,89</t>
+          <t>15,85; 32,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 24,17</t>
+          <t>11,54; 24,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 38,84</t>
+          <t>19,52; 38,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,48; 49,13</t>
+          <t>26,72; 50,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 54,56</t>
+          <t>13,0; 55,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 26,98</t>
+          <t>18,4; 27,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,6; 37,28</t>
+          <t>25,39; 37,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,84; 39,34</t>
+          <t>25,78; 39,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 44,65</t>
+          <t>17,16; 45,24</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,47; 29,27</t>
+          <t>13,92; 30,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,71; 29,15</t>
+          <t>11,9; 29,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,12; 29,75</t>
+          <t>10,54; 29,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,41; 21,67</t>
+          <t>10,39; 22,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 25,27</t>
+          <t>6,02; 26,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 35,15</t>
+          <t>10,62; 34,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 21,11</t>
+          <t>4,89; 22,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 15,11</t>
+          <t>6,75; 14,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,14; 26,0</t>
+          <t>12,99; 25,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,78; 28,09</t>
+          <t>14,33; 28,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 23,33</t>
+          <t>9,5; 22,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 16,73</t>
+          <t>9,89; 16,58</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,18; 34,21</t>
+          <t>20,23; 34,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,9; 47,8</t>
+          <t>28,87; 47,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 30,46</t>
+          <t>13,9; 29,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,3; 30,54</t>
+          <t>17,21; 30,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,67; 26,39</t>
+          <t>9,66; 25,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,56; 40,48</t>
+          <t>16,74; 41,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 19,17</t>
+          <t>3,92; 18,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,74; 44,06</t>
+          <t>27,26; 44,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,81; 28,97</t>
+          <t>18,66; 29,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27,38; 42,1</t>
+          <t>27,41; 41,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 22,33</t>
+          <t>11,42; 22,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,83; 33,11</t>
+          <t>23,08; 33,39</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,02; 31,4</t>
+          <t>21,85; 31,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,66; 25,72</t>
+          <t>15,1; 25,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,71; 26,85</t>
+          <t>17,82; 27,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,65; 27,64</t>
+          <t>17,67; 27,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,32; 30,93</t>
+          <t>17,54; 30,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,76; 32,53</t>
+          <t>19,36; 32,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,2; 24,86</t>
+          <t>15,44; 25,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,05; 28,01</t>
+          <t>19,39; 27,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,86; 29,7</t>
+          <t>22,07; 29,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,34; 26,31</t>
+          <t>18,09; 26,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,63; 24,44</t>
+          <t>17,85; 24,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,44; 25,94</t>
+          <t>19,54; 26,13</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,22; 28,08</t>
+          <t>19,7; 27,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,64; 16,86</t>
+          <t>9,65; 16,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,32</t>
+          <t>8,41; 15,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,24; 16,18</t>
+          <t>3,3; 15,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,99; 26,78</t>
+          <t>15,74; 27,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,89; 16,75</t>
+          <t>7,84; 16,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,64; 13,62</t>
+          <t>5,87; 13,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,89; 26,84</t>
+          <t>15,66; 26,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,7; 25,99</t>
+          <t>19,66; 25,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,82; 15,54</t>
+          <t>10,17; 15,58</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,01</t>
+          <t>8,16; 13,46</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,28; 18,1</t>
+          <t>5,49; 17,72</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,82; 26,77</t>
+          <t>22,95; 26,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,2; 25,66</t>
+          <t>21,21; 25,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,58; 27,28</t>
+          <t>22,46; 27,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,41; 20,79</t>
+          <t>11,41; 20,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,41</t>
+          <t>19,23; 24,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,07; 25,82</t>
+          <t>20,11; 25,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,57; 23,82</t>
+          <t>18,4; 23,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,89; 30,1</t>
+          <t>20,51; 29,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,11; 25,31</t>
+          <t>22,16; 25,42</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,42; 24,82</t>
+          <t>21,41; 24,97</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21,5; 25,1</t>
+          <t>21,42; 24,84</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,17</t>
+          <t>16,16; 23,37</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31941; 54640</t>
+          <t>32798; 55206</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30130; 52508</t>
+          <t>29566; 51062</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47068; 70552</t>
+          <t>47092; 71889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16086; 37037</t>
+          <t>15477; 36074</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20146; 38323</t>
+          <t>20660; 39668</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20900; 38630</t>
+          <t>21201; 39674</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30607; 50813</t>
+          <t>31556; 51027</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10219; 22745</t>
+          <t>10988; 23061</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56337; 87304</t>
+          <t>57285; 87415</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56999; 85793</t>
+          <t>57010; 86051</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84173; 115694</t>
+          <t>85226; 115371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30025; 52539</t>
+          <t>28459; 52175</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56491; 90202</t>
+          <t>57228; 88277</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43954; 69149</t>
+          <t>45092; 68872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71604; 97974</t>
+          <t>69432; 96238</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32796; 64246</t>
+          <t>31505; 62236</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23840; 43408</t>
+          <t>23535; 42903</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25098; 46175</t>
+          <t>24750; 45858</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31554; 52905</t>
+          <t>32631; 53593</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35346; 56613</t>
+          <t>35272; 56037</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87192; 125912</t>
+          <t>87353; 124534</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72894; 107878</t>
+          <t>74619; 109015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107435; 141981</t>
+          <t>107553; 143725</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>72892; 110425</t>
+          <t>74676; 112568</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26330; 47660</t>
+          <t>25949; 47044</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16758; 34680</t>
+          <t>16766; 34600</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13686; 29734</t>
+          <t>14248; 30079</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38637; 62247</t>
+          <t>38851; 61526</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15008; 30537</t>
+          <t>14026; 30314</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11736; 28074</t>
+          <t>11398; 26936</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7063; 20309</t>
+          <t>7284; 20413</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37013; 55372</t>
+          <t>36789; 55415</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45620; 74708</t>
+          <t>45207; 73437</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32815; 56689</t>
+          <t>32619; 57441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24580; 45077</t>
+          <t>24791; 45893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81283; 111152</t>
+          <t>82424; 111932</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45072; 71575</t>
+          <t>45671; 71928</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36948; 60273</t>
+          <t>35881; 59230</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23081; 42426</t>
+          <t>23450; 42319</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28415; 57152</t>
+          <t>26735; 55210</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15567; 32546</t>
+          <t>15532; 32491</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20340; 39788</t>
+          <t>20000; 39215</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21976; 39290</t>
+          <t>21368; 40015</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31971; 141046</t>
+          <t>33600; 144739</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66440; 96642</t>
+          <t>65913; 97637</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60302; 91385</t>
+          <t>62236; 93020</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49661; 75600</t>
+          <t>49543; 76432</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72314; 190720</t>
+          <t>73293; 193247</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14890; 32343</t>
+          <t>15384; 33461</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9642; 23997</t>
+          <t>9793; 24230</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8896; 23793</t>
+          <t>8425; 23404</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11895; 24755</t>
+          <t>11866; 25736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3035; 12332</t>
+          <t>2939; 12951</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6679; 19933</t>
+          <t>6025; 19284</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2546; 11698</t>
+          <t>2709; 12219</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7266; 15969</t>
+          <t>7130; 15774</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20941; 41422</t>
+          <t>20690; 40856</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19160; 39049</t>
+          <t>19922; 39933</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12625; 31590</t>
+          <t>12866; 30496</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21544; 36800</t>
+          <t>21743; 36467</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31258; 53004</t>
+          <t>31335; 54037</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33896; 56060</t>
+          <t>33857; 55586</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14931; 32442</t>
+          <t>14805; 31779</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23230; 41019</t>
+          <t>23115; 41076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8009; 21852</t>
+          <t>7998; 21030</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9155; 22382</t>
+          <t>9253; 22724</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3169; 14490</t>
+          <t>2965; 14276</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23108; 38072</t>
+          <t>23557; 38102</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44716; 68872</t>
+          <t>44371; 70832</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47247; 72663</t>
+          <t>47305; 72309</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19790; 40660</t>
+          <t>20801; 41081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50385; 73083</t>
+          <t>50931; 73696</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73942; 105450</t>
+          <t>73395; 106574</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42742; 70201</t>
+          <t>41211; 69173</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>62779; 95168</t>
+          <t>63159; 96176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58258; 91254</t>
+          <t>58325; 90711</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32901; 55549</t>
+          <t>31488; 54986</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34170; 59262</t>
+          <t>35259; 58738</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42960; 70265</t>
+          <t>43629; 73352</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>57465; 84478</t>
+          <t>58490; 84393</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>112692; 153089</t>
+          <t>113759; 152953</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>83475; 119744</t>
+          <t>82341; 119882</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>112306; 155696</t>
+          <t>113738; 154342</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>122794; 163880</t>
+          <t>123445; 165044</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>92786; 128891</t>
+          <t>90427; 126190</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34911; 61080</t>
+          <t>34971; 60630</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27356; 53518</t>
+          <t>27588; 52189</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20343; 101637</t>
+          <t>20710; 96543</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38214; 64003</t>
+          <t>37611; 64645</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20483; 43470</t>
+          <t>20345; 43631</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13569; 32749</t>
+          <t>14127; 31669</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>42961; 72556</t>
+          <t>42345; 70989</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>137497; 181428</t>
+          <t>137232; 180067</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>61059; 96625</t>
+          <t>63251; 96853</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47831; 79650</t>
+          <t>46372; 76482</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>56470; 162673</t>
+          <t>49359; 159228</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>432161; 506905</t>
+          <t>434510; 510003</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>300778; 363978</t>
+          <t>300958; 365159</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>318451; 384700</t>
+          <t>316701; 384864</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>221407; 403545</t>
+          <t>221500; 403377</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>195809; 249326</t>
+          <t>196389; 247541</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>190384; 244971</t>
+          <t>190759; 242807</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>191645; 245787</t>
+          <t>189877; 242026</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>301871; 435034</t>
+          <t>296499; 430214</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>644460; 737682</t>
+          <t>646055; 740870</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>506992; 587553</t>
+          <t>506861; 591211</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>525085; 613144</t>
+          <t>523190; 606579</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>547345; 784691</t>
+          <t>547157; 791217</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P68-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P68-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,94; 33,56</t>
+          <t>18,89; 33,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,5; 40,58</t>
+          <t>23,95; 40,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,58; 52,79</t>
+          <t>34,76; 51,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 18,58</t>
+          <t>9,03; 18,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,62; 35,75</t>
+          <t>18,17; 35,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,24; 45,36</t>
+          <t>25,05; 46,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,25; 50,53</t>
+          <t>30,78; 50,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 15,98</t>
+          <t>7,51; 14,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 31,73</t>
+          <t>20,53; 31,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,73; 40,35</t>
+          <t>26,07; 40,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,94; 48,65</t>
+          <t>35,57; 49,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 15,41</t>
+          <t>9,01; 15,4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,16; 32,64</t>
+          <t>21,43; 32,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,18; 39,99</t>
+          <t>25,66; 41,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,77; 56,51</t>
+          <t>41,15; 56,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,05; 27,75</t>
+          <t>14,76; 27,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 32,5</t>
+          <t>17,59; 33,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,17; 37,38</t>
+          <t>19,95; 36,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,7; 47,14</t>
+          <t>28,05; 47,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,39; 35,57</t>
+          <t>22,47; 34,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 30,94</t>
+          <t>21,87; 30,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,3; 36,96</t>
+          <t>24,61; 36,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37,87; 50,61</t>
+          <t>38,42; 49,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,56; 29,48</t>
+          <t>18,79; 28,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 26,94</t>
+          <t>15,15; 27,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 24,16</t>
+          <t>12,18; 24,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 24,48</t>
+          <t>11,14; 25,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,47; 41,91</t>
+          <t>26,97; 41,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,97; 32,36</t>
+          <t>15,61; 33,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 32,7</t>
+          <t>13,96; 31,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 24,49</t>
+          <t>8,58; 23,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,44; 45,85</t>
+          <t>30,85; 45,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 27,37</t>
+          <t>17,28; 27,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 25,47</t>
+          <t>14,5; 24,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,02; 22,26</t>
+          <t>11,55; 21,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,79; 41,82</t>
+          <t>30,47; 40,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,43; 32,18</t>
+          <t>20,38; 32,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 41,51</t>
+          <t>25,44; 42,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 37,72</t>
+          <t>20,15; 37,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 32,73</t>
+          <t>17,82; 34,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,54; 24,13</t>
+          <t>11,32; 23,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,52; 38,28</t>
+          <t>20,52; 38,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 50,03</t>
+          <t>26,85; 48,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 55,99</t>
+          <t>23,1; 36,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 27,26</t>
+          <t>18,96; 27,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,39; 37,95</t>
+          <t>25,7; 38,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,78; 39,78</t>
+          <t>25,56; 39,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,16; 45,24</t>
+          <t>21,98; 32,83</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,92; 30,28</t>
+          <t>13,93; 29,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,9; 29,44</t>
+          <t>11,51; 29,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 29,27</t>
+          <t>10,47; 28,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 22,53</t>
+          <t>10,96; 21,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 26,54</t>
+          <t>6,13; 27,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 34,0</t>
+          <t>10,47; 34,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 22,05</t>
+          <t>3,82; 20,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 14,92</t>
+          <t>7,69; 15,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,99; 25,65</t>
+          <t>13,46; 25,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 28,72</t>
+          <t>14,0; 27,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,5; 22,52</t>
+          <t>9,93; 22,3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,89; 16,58</t>
+          <t>10,68; 17,95</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,23; 34,88</t>
+          <t>20,23; 34,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,87; 47,39</t>
+          <t>28,65; 47,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,9; 29,84</t>
+          <t>13,35; 29,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,21; 30,59</t>
+          <t>18,23; 31,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,66; 25,39</t>
+          <t>10,87; 27,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,74; 41,1</t>
+          <t>17,75; 41,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,92; 18,89</t>
+          <t>4,6; 19,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,26; 44,1</t>
+          <t>26,25; 43,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,66; 29,79</t>
+          <t>18,7; 29,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27,41; 41,9</t>
+          <t>27,14; 42,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,42; 22,56</t>
+          <t>11,61; 22,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,08; 33,39</t>
+          <t>23,24; 33,79</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,85; 31,73</t>
+          <t>21,55; 31,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,1; 25,35</t>
+          <t>14,97; 25,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,82; 27,13</t>
+          <t>18,09; 27,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,67; 27,48</t>
+          <t>18,07; 28,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,54; 30,62</t>
+          <t>18,13; 31,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,36; 32,24</t>
+          <t>19,5; 32,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,44; 25,95</t>
+          <t>15,4; 24,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,39; 27,98</t>
+          <t>18,61; 26,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,07; 29,68</t>
+          <t>21,85; 29,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,09; 26,34</t>
+          <t>18,41; 26,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,22</t>
+          <t>17,68; 24,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,54; 26,13</t>
+          <t>19,33; 25,66</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,7; 27,49</t>
+          <t>19,74; 28,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,65; 16,74</t>
+          <t>9,62; 16,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,41; 15,92</t>
+          <t>8,73; 16,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,3; 15,37</t>
+          <t>11,44; 18,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,74; 27,05</t>
+          <t>15,91; 25,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,84; 16,81</t>
+          <t>8,03; 17,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 13,17</t>
+          <t>5,67; 13,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,66; 26,26</t>
+          <t>14,68; 22,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,66; 25,8</t>
+          <t>19,48; 26,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,17; 15,58</t>
+          <t>9,85; 15,59</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,16; 13,46</t>
+          <t>8,05; 13,54</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 17,72</t>
+          <t>13,75; 18,99</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,95; 26,94</t>
+          <t>22,72; 26,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,21; 25,74</t>
+          <t>21,07; 25,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,46; 27,29</t>
+          <t>22,39; 27,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,41; 20,78</t>
+          <t>18,15; 22,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,23; 24,23</t>
+          <t>18,7; 24,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,11; 25,59</t>
+          <t>20,1; 25,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,4; 23,45</t>
+          <t>18,53; 23,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,51; 29,77</t>
+          <t>21,32; 25,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,16; 25,42</t>
+          <t>22,24; 25,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,41; 24,97</t>
+          <t>21,35; 24,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21,42; 24,84</t>
+          <t>21,43; 24,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,37</t>
+          <t>20,0; 22,99</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24069</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39824</t>
+          <t>42418</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32798; 55206</t>
+          <t>31082; 55057</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29566; 51062</t>
+          <t>30128; 51529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47092; 71889</t>
+          <t>47335; 70330</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15477; 36074</t>
+          <t>18276; 38217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20660; 39668</t>
+          <t>20167; 39548</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21201; 39674</t>
+          <t>21911; 40294</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31556; 51027</t>
+          <t>31084; 51103</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10988; 23061</t>
+          <t>11476; 22258</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57285; 87415</t>
+          <t>56558; 87311</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57010; 86051</t>
+          <t>55608; 85882</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85226; 115371</t>
+          <t>84362; 116877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28459; 52175</t>
+          <t>31997; 54680</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46280</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45443</t>
+          <t>46506</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91723</t>
+          <t>94512</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57228; 88277</t>
+          <t>57952; 87407</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45092; 68872</t>
+          <t>44191; 71906</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69432; 96238</t>
+          <t>70079; 96893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31505; 62236</t>
+          <t>34534; 64423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23535; 42903</t>
+          <t>23225; 44299</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24750; 45858</t>
+          <t>24477; 45388</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32631; 53593</t>
+          <t>31888; 53453</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35272; 56037</t>
+          <t>37188; 56787</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87353; 124534</t>
+          <t>88032; 123846</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74619; 109015</t>
+          <t>72581; 107471</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107553; 143725</t>
+          <t>109105; 141785</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74676; 112568</t>
+          <t>75057; 113607</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>49597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95422</t>
+          <t>96560</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25949; 47044</t>
+          <t>26453; 48115</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16766; 34600</t>
+          <t>17438; 35671</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14248; 30079</t>
+          <t>13687; 30958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38851; 61526</t>
+          <t>39859; 61359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14026; 30314</t>
+          <t>14625; 31355</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11398; 26936</t>
+          <t>11501; 26105</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7284; 20413</t>
+          <t>7154; 19476</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36789; 55415</t>
+          <t>37959; 56111</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45207; 73437</t>
+          <t>46373; 73430</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32619; 57441</t>
+          <t>32697; 56094</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24791; 45893</t>
+          <t>23820; 44604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82424; 111932</t>
+          <t>82515; 110711</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>54166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>121006</t>
+          <t>107451</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45671; 71928</t>
+          <t>45567; 73364</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35881; 59230</t>
+          <t>36299; 60622</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23450; 42319</t>
+          <t>22599; 42152</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26735; 55210</t>
+          <t>37955; 73764</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15532; 32491</t>
+          <t>15244; 32121</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20000; 39215</t>
+          <t>21021; 39815</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21368; 40015</t>
+          <t>21474; 39171</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33600; 144739</t>
+          <t>41768; 66082</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65913; 97637</t>
+          <t>67917; 99537</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62236; 93020</t>
+          <t>63002; 94252</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49543; 76432</t>
+          <t>49116; 75919</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73293; 193247</t>
+          <t>86564; 129281</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>35245</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15384; 33461</t>
+          <t>15398; 32533</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9793; 24230</t>
+          <t>9472; 23984</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8425; 23404</t>
+          <t>8371; 23181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11866; 25736</t>
+          <t>14928; 29661</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2939; 12951</t>
+          <t>2991; 13376</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6025; 19284</t>
+          <t>5935; 19384</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2709; 12219</t>
+          <t>2120; 11424</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7130; 15774</t>
+          <t>9068; 18789</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20690; 40856</t>
+          <t>21440; 41391</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19922; 39933</t>
+          <t>19460; 38867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12866; 30496</t>
+          <t>13448; 30192</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21743; 36467</t>
+          <t>27119; 45588</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61831</t>
+          <t>63451</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31335; 54037</t>
+          <t>31344; 53629</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33857; 55586</t>
+          <t>33604; 56254</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14805; 31779</t>
+          <t>14216; 31278</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23115; 41076</t>
+          <t>24666; 42519</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7998; 21030</t>
+          <t>9002; 22729</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9253; 22724</t>
+          <t>9816; 22828</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2965; 14276</t>
+          <t>3473; 14827</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23557; 38102</t>
+          <t>22931; 37908</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44371; 70832</t>
+          <t>44451; 70875</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47305; 72309</t>
+          <t>46846; 73619</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20801; 41081</t>
+          <t>21131; 40404</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50931; 73696</t>
+          <t>51758; 75245</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>85851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>80718</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>143705</t>
+          <t>166568</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73395; 106574</t>
+          <t>72372; 105106</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41211; 69173</t>
+          <t>40853; 70470</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63159; 96176</t>
+          <t>64131; 96699</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58325; 90711</t>
+          <t>69236; 108083</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31488; 54986</t>
+          <t>32557; 56792</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35259; 58738</t>
+          <t>35515; 59169</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43629; 73352</t>
+          <t>43539; 69833</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>58490; 84393</t>
+          <t>66210; 95467</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>113759; 152953</t>
+          <t>112618; 152514</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>82341; 119882</t>
+          <t>83790; 119727</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113738; 154342</t>
+          <t>112626; 155491</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>123445; 165044</t>
+          <t>142794; 189561</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56757</t>
+          <t>66654</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>54710</t>
+          <t>57483</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>111467</t>
+          <t>124138</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>90427; 126190</t>
+          <t>90611; 129267</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34971; 60630</t>
+          <t>34847; 60489</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27588; 52189</t>
+          <t>28635; 52895</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20710; 96543</t>
+          <t>52042; 83749</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>37611; 64645</t>
+          <t>38015; 62014</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20345; 43631</t>
+          <t>20840; 44552</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14127; 31669</t>
+          <t>13625; 32225</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>42345; 70989</t>
+          <t>45701; 70173</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>137232; 180067</t>
+          <t>135932; 181484</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>63251; 96853</t>
+          <t>61234; 96928</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>46372; 76482</t>
+          <t>45771; 76964</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49359; 159228</t>
+          <t>105333; 145556</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>339505</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>354215</t>
+          <t>345334</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>693720</t>
+          <t>730344</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>434510; 510003</t>
+          <t>430098; 508849</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>300958; 365159</t>
+          <t>298880; 363016</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>316701; 384864</t>
+          <t>315797; 384409</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>221500; 403377</t>
+          <t>345993; 427477</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>196389; 247541</t>
+          <t>190991; 247029</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>190759; 242807</t>
+          <t>190709; 245637</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>189877; 242026</t>
+          <t>191223; 242145</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>296499; 430214</t>
+          <t>318644; 374504</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>646055; 740870</t>
+          <t>648329; 738299</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>506861; 591211</t>
+          <t>505548; 585496</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>523190; 606579</t>
+          <t>523285; 608126</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>547157; 791217</t>
+          <t>680340; 782010</t>
         </is>
       </c>
     </row>
